--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-eflow-rx-close-operation-input-parameters.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-eflow-rx-close-operation-input-parameters.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="207">
   <si>
     <t>Property</t>
   </si>
@@ -383,10 +383,6 @@
     <t>closed</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}</t>
   </si>
@@ -427,16 +423,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -476,9 +462,6 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -492,8 +475,8 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
-    <t>ele-1
-inv-1</t>
+    <t xml:space="preserve">inv-1
+</t>
   </si>
   <si>
     <t>Parameters.parameter.resource</t>
@@ -510,13 +493,6 @@
   </si>
   <si>
     <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -1033,7 +1009,7 @@
     <col min="26" max="26" width="35.15234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1790,24 +1766,24 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1830,13 +1806,13 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1887,7 +1863,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -1910,14 +1886,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1936,16 +1912,16 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1983,19 +1959,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2007,7 +1983,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2018,14 +1994,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2044,19 +2020,19 @@
         <v>86</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2105,7 +2081,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2117,21 +2093,21 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2154,17 +2130,15 @@
         <v>86</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2213,7 +2187,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>85</v>
@@ -2236,10 +2210,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2262,13 +2236,13 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2319,7 +2293,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2328,7 +2302,7 @@
         <v>85</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>97</v>
@@ -2337,15 +2311,15 @@
         <v>76</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2368,16 +2342,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2427,7 +2401,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2436,7 +2410,7 @@
         <v>85</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>76</v>
@@ -2445,15 +2419,15 @@
         <v>76</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>159</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2479,13 +2453,13 @@
         <v>76</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2535,7 +2509,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2547,7 +2521,7 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>76</v>
@@ -2558,13 +2532,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>113</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>76</v>
@@ -2652,24 +2626,24 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2692,13 +2666,13 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2749,7 +2723,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2772,14 +2746,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2798,16 +2772,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2845,19 +2819,19 @@
         <v>76</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -2869,7 +2843,7 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>76</v>
@@ -2880,14 +2854,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -2906,19 +2880,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -2967,7 +2941,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -2979,21 +2953,21 @@
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3016,17 +2990,15 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3036,7 +3008,7 @@
         <v>76</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>76</v>
@@ -3075,7 +3047,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>85</v>
@@ -3098,10 +3070,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3124,13 +3096,13 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3181,7 +3153,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3190,7 +3162,7 @@
         <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>97</v>
@@ -3199,15 +3171,15 @@
         <v>76</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3230,16 +3202,16 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3289,7 +3261,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3298,7 +3270,7 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>76</v>
@@ -3307,15 +3279,15 @@
         <v>76</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>159</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3341,13 +3313,13 @@
         <v>76</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3395,7 +3367,7 @@
         <v>118</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3407,7 +3379,7 @@
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>76</v>
@@ -3418,10 +3390,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3444,13 +3416,13 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3501,7 +3473,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3524,14 +3496,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3550,16 +3522,16 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3597,19 +3569,19 @@
         <v>76</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3621,7 +3593,7 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>76</v>
@@ -3632,14 +3604,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3658,19 +3630,19 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -3719,7 +3691,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3731,21 +3703,21 @@
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3768,17 +3740,15 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -3827,7 +3797,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>85</v>
@@ -3850,10 +3820,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3876,13 +3846,13 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3933,7 +3903,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -3942,7 +3912,7 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
@@ -3951,15 +3921,15 @@
         <v>76</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3982,16 +3952,16 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4041,7 +4011,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4050,7 +4020,7 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>76</v>
@@ -4059,15 +4029,15 @@
         <v>76</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>159</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4093,13 +4063,13 @@
         <v>76</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4149,7 +4119,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4161,7 +4131,7 @@
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>76</v>
@@ -4172,13 +4142,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>76</v>
@@ -4203,13 +4173,13 @@
         <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4259,7 +4229,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4271,7 +4241,7 @@
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>76</v>
@@ -4282,10 +4252,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4308,13 +4278,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4365,7 +4335,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4388,14 +4358,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4414,16 +4384,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4461,19 +4431,19 @@
         <v>76</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4485,7 +4455,7 @@
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>76</v>
@@ -4496,14 +4466,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4522,19 +4492,19 @@
         <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -4583,7 +4553,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -4595,21 +4565,21 @@
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4632,17 +4602,15 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -4652,7 +4620,7 @@
         <v>76</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>76</v>
@@ -4691,7 +4659,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>85</v>
@@ -4714,10 +4682,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4740,13 +4708,13 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4797,7 +4765,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -4806,7 +4774,7 @@
         <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>97</v>
@@ -4815,15 +4783,15 @@
         <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4846,16 +4814,16 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -4905,7 +4873,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -4923,15 +4891,15 @@
         <v>76</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4957,13 +4925,13 @@
         <v>76</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5013,7 +4981,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5025,7 +4993,7 @@
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>76</v>
@@ -5036,13 +5004,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>76</v>
@@ -5067,13 +5035,13 @@
         <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5123,7 +5091,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5135,7 +5103,7 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>76</v>
@@ -5146,10 +5114,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5172,13 +5140,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5229,7 +5197,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5252,14 +5220,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5278,16 +5246,16 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5325,19 +5293,19 @@
         <v>76</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5349,7 +5317,7 @@
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
@@ -5360,14 +5328,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5386,19 +5354,19 @@
         <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -5447,7 +5415,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -5459,21 +5427,21 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5496,17 +5464,15 @@
         <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -5516,7 +5482,7 @@
         <v>76</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>76</v>
@@ -5555,7 +5521,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>85</v>
@@ -5578,10 +5544,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5604,13 +5570,13 @@
         <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5661,7 +5627,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -5670,7 +5636,7 @@
         <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>97</v>
@@ -5679,15 +5645,15 @@
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5710,16 +5676,16 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5769,7 +5735,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -5787,15 +5753,15 @@
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5821,13 +5787,13 @@
         <v>76</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5877,7 +5843,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -5889,7 +5855,7 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>76</v>
